--- a/Data/EventData/SDGE_2024.xlsx
+++ b/Data/EventData/SDGE_2024.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_11205F067F7A671B34516787D6747528E49DA5B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43A47631-80F4-4F33-9754-56B8825F27CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5415D2A-E148-435A-83B5-A4E3C87613F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interactive (2024)" sheetId="3" r:id="rId1"/>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="179">
   <si>
     <t>Utility Name</t>
   </si>
@@ -1054,9 +1054,6 @@
   </si>
   <si>
     <t>Voltage Regulator</t>
-  </si>
-  <si>
-    <t>This report includes SDG&amp;E’s preliminary assessment of the cause of the ignition; the cause of any ignition may remain subject to ongoing investigation by the appropriate fire investigation agency</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +1990,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2235,9 +2232,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2348,7 +2342,7 @@
     <cellStyle name="Total" xfId="16" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -2367,13 +2361,6 @@
       <fill>
         <patternFill>
           <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2723,81 +2710,81 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z35"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z33"/>
+  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="15" customWidth="1"/>
-    <col min="2" max="3" width="8.140625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="51" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="47" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="15" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" style="15" customWidth="1"/>
+    <col min="2" max="3" width="8.109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" style="51" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" style="47" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" style="47" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" style="15" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" style="15" customWidth="1"/>
     <col min="13" max="13" width="18" style="15" customWidth="1"/>
-    <col min="14" max="14" width="23.42578125" style="47" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" style="15" customWidth="1"/>
+    <col min="14" max="14" width="23.44140625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" style="15" customWidth="1"/>
     <col min="16" max="16" width="10" style="74" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="15" customWidth="1"/>
+    <col min="17" max="17" width="15.5546875" style="15" customWidth="1"/>
     <col min="18" max="18" width="17" style="15" customWidth="1"/>
     <col min="19" max="19" width="11" style="15" customWidth="1"/>
-    <col min="20" max="20" width="10.140625" style="15" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" style="15" customWidth="1"/>
+    <col min="20" max="20" width="10.109375" style="15" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" style="15" customWidth="1"/>
     <col min="22" max="22" width="23" style="15" customWidth="1"/>
     <col min="23" max="23" width="26" style="15" customWidth="1"/>
-    <col min="24" max="24" width="20.140625" style="15" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" style="15" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="15" customWidth="1"/>
-    <col min="27" max="16384" width="9.42578125" style="15"/>
+    <col min="24" max="24" width="20.109375" style="15" customWidth="1"/>
+    <col min="25" max="25" width="17.5546875" style="15" customWidth="1"/>
+    <col min="26" max="26" width="12.5546875" style="15" customWidth="1"/>
+    <col min="27" max="16384" width="9.44140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="102" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="105" t="s">
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="108" t="s">
+      <c r="L1" s="105"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="111" t="s">
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="112"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="93" t="s">
+      <c r="T1" s="111"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="94"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="96"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="95"/>
     </row>
-    <row r="2" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101"/>
+    <row r="2" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="100"/>
       <c r="B2" s="68" t="s">
         <v>7</v>
       </c>
@@ -2874,7 +2861,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
         <v>30</v>
       </c>
@@ -2950,7 +2937,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
         <v>30</v>
       </c>
@@ -3024,7 +3011,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="63" t="s">
         <v>30</v>
       </c>
@@ -3041,7 +3028,7 @@
         <v>45420</v>
       </c>
       <c r="F5" s="50">
-        <v>1836</v>
+        <v>0</v>
       </c>
       <c r="G5" s="35">
         <v>33.165999999999997</v>
@@ -3098,7 +3085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="63" t="s">
         <v>30</v>
       </c>
@@ -3174,7 +3161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="63" t="s">
         <v>30</v>
       </c>
@@ -3248,7 +3235,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
         <v>30</v>
       </c>
@@ -3324,7 +3311,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
         <v>30</v>
       </c>
@@ -3400,7 +3387,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="63" t="s">
         <v>30</v>
       </c>
@@ -3476,7 +3463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
         <v>30</v>
       </c>
@@ -3552,7 +3539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="63" t="s">
         <v>30</v>
       </c>
@@ -3628,7 +3615,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="63" t="s">
         <v>30</v>
       </c>
@@ -3700,7 +3687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="63" t="s">
         <v>30</v>
       </c>
@@ -3768,7 +3755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="63" t="s">
         <v>30</v>
       </c>
@@ -3842,7 +3829,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="63" t="s">
         <v>30</v>
       </c>
@@ -3920,7 +3907,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="63" t="s">
         <v>30</v>
       </c>
@@ -3996,7 +3983,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
         <v>30</v>
       </c>
@@ -4072,7 +4059,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="63" t="s">
         <v>30</v>
       </c>
@@ -4146,7 +4133,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="63" t="s">
         <v>30</v>
       </c>
@@ -4222,7 +4209,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="63" t="s">
         <v>30</v>
       </c>
@@ -4296,7 +4283,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="63" t="s">
         <v>30</v>
       </c>
@@ -4370,7 +4357,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="63" t="s">
         <v>30</v>
       </c>
@@ -4444,7 +4431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="63" t="s">
         <v>30</v>
       </c>
@@ -4516,7 +4503,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="63" t="s">
         <v>30</v>
       </c>
@@ -4533,7 +4520,7 @@
         <v>45564</v>
       </c>
       <c r="F25" s="50">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="G25" s="35">
         <v>32.646999999999998</v>
@@ -4588,7 +4575,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="63" t="s">
         <v>30</v>
       </c>
@@ -4664,7 +4651,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="63" t="s">
         <v>30</v>
       </c>
@@ -4736,7 +4723,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="63" t="s">
         <v>30</v>
       </c>
@@ -4806,7 +4793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="63" t="s">
         <v>30</v>
       </c>
@@ -4884,7 +4871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="63" t="s">
         <v>30</v>
       </c>
@@ -4952,7 +4939,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="63" t="s">
         <v>30</v>
       </c>
@@ -5024,7 +5011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="63" t="s">
         <v>30</v>
       </c>
@@ -5094,7 +5081,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="63" t="s">
         <v>30</v>
       </c>
@@ -5168,37 +5155,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="92"/>
-      <c r="R35" s="92"/>
-      <c r="S35" s="92"/>
-      <c r="T35" s="92"/>
-      <c r="U35" s="92"/>
-      <c r="V35" s="92"/>
-      <c r="W35" s="92"/>
-    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="8">
-    <mergeCell ref="A35:W35"/>
+  <mergeCells count="7">
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="A1:A2"/>
@@ -5209,33 +5168,28 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="M3:M33">
-    <cfRule type="expression" dxfId="8" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
       <formula>IF(L3&lt;&gt;"Fire Agency",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O11">
-    <cfRule type="expression" dxfId="7" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="38" stopIfTrue="1">
       <formula>IF($R3&lt;&gt;"Overhead",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O12">
-    <cfRule type="expression" dxfId="6" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="43" stopIfTrue="1">
       <formula>IF($R15&lt;&gt;"Overhead",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O33">
-    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
       <formula>IF($R13&lt;&gt;"Overhead",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T3:U25">
-    <cfRule type="expression" dxfId="4" priority="12" stopIfTrue="1">
+  <conditionalFormatting sqref="T3:U33">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>IF($S3&lt;&gt;"Yes",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T26:U33">
-    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
-      <formula>IF($S26&lt;&gt;"Yes",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W33">
@@ -5305,13 +5259,13 @@
           <x14:formula1>
             <xm:f>'Drop Downs'!$S:$S</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B29 B31:B34 B36:B1048576</xm:sqref>
+          <xm:sqref>B1:B29 B31:B33 B34:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000011000000}">
           <x14:formula1>
             <xm:f>'Drop Downs'!$V:$V</xm:f>
           </x14:formula1>
-          <xm:sqref>P1:P29 P31:P34 P36:P1048576</xm:sqref>
+          <xm:sqref>P1:P29 P31:P33 P34:P1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5322,7 +5276,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5333,28 +5287,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V18"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="76.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="53" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.42578125" style="1"/>
+    <col min="13" max="13" width="29.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G1" s="83"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>142</v>
       </c>
@@ -5416,7 +5370,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>148</v>
       </c>
@@ -5479,7 +5433,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>151</v>
       </c>
@@ -5536,7 +5490,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>157</v>
       </c>
@@ -5578,7 +5532,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>160</v>
       </c>
@@ -5620,7 +5574,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>164</v>
       </c>
@@ -5656,7 +5610,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -5689,7 +5643,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G9" s="82" t="s">
         <v>99</v>
       </c>
@@ -5710,7 +5664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G10" s="83" t="s">
         <v>171</v>
       </c>
@@ -5728,7 +5682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G11" s="83"/>
       <c r="M11" s="1" t="s">
         <v>174</v>
@@ -5741,7 +5695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G12" s="83"/>
       <c r="M12" s="1" t="s">
         <v>175</v>
@@ -5754,7 +5708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G13" s="83"/>
       <c r="M13" s="1" t="s">
         <v>176</v>
@@ -5767,7 +5721,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G14" s="83" t="s">
         <v>166</v>
       </c>
@@ -5779,7 +5733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G15" s="83"/>
       <c r="M15" s="1" t="s">
         <v>72</v>
@@ -5789,7 +5743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="G16" s="83"/>
       <c r="M16" s="1" t="s">
         <v>107</v>
@@ -5799,7 +5753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="7:20" x14ac:dyDescent="0.3">
       <c r="G17" s="83"/>
       <c r="M17" s="1" t="s">
         <v>178</v>
@@ -5809,7 +5763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="7:20" x14ac:dyDescent="0.3">
       <c r="G18" s="83"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
